--- a/output/2026-09-20_04_Croazia_Sibensko-kninska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-20_04_Croazia_Sibensko-kninska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -586,7 +586,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>BORDERLINE - azienda di costruzioni che vende anche ferramenta/viteria/utensili (attività primaria: costruzioni). Esistenza confermata via Fina/Fininfo (OIB 15449982602). Email reperita da fonte terza, non dal sito ufficiale (WebFetch bloccato) - verificare prima dell'uso commerciale.</t>
+          <t>BORDERLINE - azienda di costruzioni che vende anche ferramenta/viteria/utensili (attività primaria: costruzioni). Esistenza confermata via Fina/Fininfo (OIB 15449982602). Email reperita da fonte terza, non dal sito ufficiale (WebFetch bloccato) - verificare prima dell'uso commerciale. [DUPLICATO — vedi anche: 2026-09-20_01_Croazia_Šibensko-kninska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">

--- a/output/2026-09-20_04_Croazia_Sibensko-kninska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-20_04_Croazia_Sibensko-kninska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -507,7 +507,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-20_04_Croazia_Sibensko-kninska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-20_04_Croazia_Sibensko-kninska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Verificato integralmente via WebSearch: indirizzo (Ulica Ivana Meštrovića 11 I, 22000 Šibenik), telefono, email e orari coincidono con i dati grezzi. Distributore altamente coerente col settore metalworking.</t>
+          <t>Verificato integralmente via WebSearch: indirizzo (Ulica Ivana Meštrovića 11 I, 22000 Šibenik), telefono, email e orari coincidono con i dati grezzi. Distributore altamente coerente col settore metalworking. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
